--- a/Apostas_Diarias/Apostas_20260410.xlsx
+++ b/Apostas_Diarias/Apostas_20260410.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_2B590F4F95D6CE120D00D1F0502E00326089FB08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5F1C76B-DB83-4FA7-9C65-B3D9CC3DEAD2}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_2B590F4F95E6C73A4100DBF05037D0B2697DFADE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825A05D9-F99E-4585-98B6-68F361FA93FC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>Data</t>
   </si>
@@ -74,31 +74,37 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>12:30:00</t>
-  </si>
-  <si>
-    <t>SLOVENIA 1</t>
-  </si>
-  <si>
-    <t>NK Primorje x Koper</t>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>FINLAND 1</t>
+  </si>
+  <si>
+    <t>TPS x Lahti</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>14:30:00</t>
-  </si>
-  <si>
-    <t>FRANCE 3</t>
-  </si>
-  <si>
-    <t>Sochaux x Fleury Merogis</t>
-  </si>
-  <si>
-    <t>Stade Briochin x Villefranche Beaujolais</t>
-  </si>
-  <si>
-    <t>Valenciennes x Versailles 78 FC</t>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>FRANCE 2</t>
+  </si>
+  <si>
+    <t>Annecy x Montpellier</t>
+  </si>
+  <si>
+    <t>Clermont x Nancy</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>SCOTLAND 2</t>
+  </si>
+  <si>
+    <t>Queens Park x Ross Co</t>
   </si>
 </sst>
 </file>
@@ -445,7 +451,7 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -488,6 +494,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -509,12 +518,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="H2">
-        <v>13.5</v>
+        <f>G2</f>
+        <v>11</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -523,7 +534,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>37.400000000000006</v>
+        <v>46.75</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -549,21 +560,23 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="H3">
-        <v>19.5</v>
+        <f t="shared" ref="H3:H5" si="0">G3</f>
+        <v>10.5</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I5" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J5" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J5" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K5" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>25.270270270270274</v>
+        <f t="shared" ref="K3:K5" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>49.210526315789473</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -589,21 +602,23 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="H4">
-        <v>12.5</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
+        <f t="shared" si="3"/>
+        <v>46.75</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -617,33 +632,35 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="H5">
-        <v>13.5</v>
+        <f t="shared" si="0"/>
+        <v>9.6</v>
       </c>
       <c r="I5">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
-        <v>37.400000000000006</v>
+        <f t="shared" si="3"/>
+        <v>54.360465116279073</v>
       </c>
       <c r="L5">
         <v>1</v>

--- a/Apostas_Diarias/Apostas_20260410.xlsx
+++ b/Apostas_Diarias/Apostas_20260410.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_2B590F4F95E6C73A4100DBF05037D0B2697DFADE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825A05D9-F99E-4585-98B6-68F361FA93FC}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_2B590F4F95D6CE120D00D1F0502E00326089FB08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5F1C76B-DB83-4FA7-9C65-B3D9CC3DEAD2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>Data</t>
   </si>
@@ -74,37 +74,31 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>12:00:00</t>
-  </si>
-  <si>
-    <t>FINLAND 1</t>
-  </si>
-  <si>
-    <t>TPS x Lahti</t>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>SLOVENIA 1</t>
+  </si>
+  <si>
+    <t>NK Primorje x Koper</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Annecy x Montpellier</t>
-  </si>
-  <si>
-    <t>Clermont x Nancy</t>
-  </si>
-  <si>
-    <t>15:45:00</t>
-  </si>
-  <si>
-    <t>SCOTLAND 2</t>
-  </si>
-  <si>
-    <t>Queens Park x Ross Co</t>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>FRANCE 3</t>
+  </si>
+  <si>
+    <t>Sochaux x Fleury Merogis</t>
+  </si>
+  <si>
+    <t>Stade Briochin x Villefranche Beaujolais</t>
+  </si>
+  <si>
+    <t>Valenciennes x Versailles 78 FC</t>
   </si>
 </sst>
 </file>
@@ -451,7 +445,7 @@
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -494,9 +488,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -518,14 +509,12 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -534,7 +523,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>46.75</v>
+        <v>37.400000000000006</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -560,23 +549,21 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H5" si="0">G3</f>
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I5" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J5" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J5" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K5" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>49.210526315789473</v>
+        <f t="shared" ref="K3:K5" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>25.270270270270274</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -602,23 +589,21 @@
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="H4">
+        <v>12.5</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <v>40.652173913043484</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -632,35 +617,33 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="H5">
+        <v>13.5</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
         <f t="shared" si="0"/>
-        <v>9.6</v>
-      </c>
-      <c r="I5">
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="3"/>
-        <v>54.360465116279073</v>
+        <v>37.400000000000006</v>
       </c>
       <c r="L5">
         <v>1</v>
